--- a/artfynd/A 56368-2024 artfynd.xlsx
+++ b/artfynd/A 56368-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124711643</v>
+        <v>124711558</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490997</v>
+        <v>490998</v>
       </c>
       <c r="R2" t="n">
         <v>6949559</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124711558</v>
+        <v>124711643</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490998</v>
+        <v>490997</v>
       </c>
       <c r="R3" t="n">
         <v>6949559</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 56368-2024 artfynd.xlsx
+++ b/artfynd/A 56368-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124711558</v>
+        <v>124711643</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490998</v>
+        <v>490997</v>
       </c>
       <c r="R2" t="n">
         <v>6949559</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124711643</v>
+        <v>124711558</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490997</v>
+        <v>490998</v>
       </c>
       <c r="R3" t="n">
         <v>6949559</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 56368-2024 artfynd.xlsx
+++ b/artfynd/A 56368-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124711643</v>
+        <v>124711558</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490997</v>
+        <v>490998</v>
       </c>
       <c r="R2" t="n">
         <v>6949559</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,118 +784,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>124711558</v>
-      </c>
-      <c r="B3" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Lilltjärnen, Lilltjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>490998</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6949559</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Hackås</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Anders Wännström</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Anders Wännström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56368-2024 artfynd.xlsx
+++ b/artfynd/A 56368-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126752064</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126752127</v>
       </c>
       <c r="B4" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126753143</v>
       </c>
       <c r="B5" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56368-2024 artfynd.xlsx
+++ b/artfynd/A 56368-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126752064</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126752127</v>
       </c>
       <c r="B4" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126753143</v>
       </c>
       <c r="B5" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56368-2024 artfynd.xlsx
+++ b/artfynd/A 56368-2024 artfynd.xlsx
@@ -1004,7 +1004,7 @@
         <v>126753143</v>
       </c>
       <c r="B5" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56368-2024 artfynd.xlsx
+++ b/artfynd/A 56368-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126752064</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126752127</v>
       </c>
       <c r="B4" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126753143</v>
       </c>
       <c r="B5" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56368-2024 artfynd.xlsx
+++ b/artfynd/A 56368-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126752064</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126752127</v>
       </c>
       <c r="B4" t="n">
-        <v>75142</v>
+        <v>75135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126753143</v>
       </c>
       <c r="B5" t="n">
-        <v>98364</v>
+        <v>98353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
